--- a/club_ranges.xlsx
+++ b/club_ranges.xlsx
@@ -457,14 +457,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>42.36425000000003</v>
+        <v>42.496</v>
       </c>
       <c r="C2" t="n">
-        <v>84.23309999999995</v>
+        <v>83.41199999999998</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>42-84</t>
+          <t>42-83</t>
         </is>
       </c>
     </row>
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>84.45100000000008</v>
+        <v>81.83624999999995</v>
       </c>
       <c r="C3" t="n">
-        <v>114.0783999999999</v>
+        <v>109.8654000000001</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>84-114</t>
+          <t>81-109</t>
         </is>
       </c>
     </row>
@@ -493,14 +493,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>108.0975</v>
+        <v>106.2040000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>128.4039999999998</v>
+        <v>127.5999999999999</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>108-128</t>
+          <t>106-127</t>
         </is>
       </c>
     </row>
@@ -511,14 +511,14 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>130.5236</v>
+        <v>127.8786</v>
       </c>
       <c r="C5" t="n">
-        <v>144.776</v>
+        <v>142.8230999999999</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>130-144</t>
+          <t>127-142</t>
         </is>
       </c>
     </row>
@@ -529,14 +529,14 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>138.0354000000001</v>
+        <v>137.7482999999998</v>
       </c>
       <c r="C6" t="n">
-        <v>154.4812000000001</v>
+        <v>153.1431999999999</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>138-154</t>
+          <t>137-153</t>
         </is>
       </c>
     </row>
@@ -547,14 +547,14 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>151.29845</v>
+        <v>150.2533499999999</v>
       </c>
       <c r="C7" t="n">
-        <v>166.5779</v>
+        <v>165.37325</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>151-166</t>
+          <t>150-165</t>
         </is>
       </c>
     </row>
@@ -565,14 +565,14 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>161.4381999999998</v>
+        <v>161.3094</v>
       </c>
       <c r="C8" t="n">
-        <v>173.7279999999999</v>
+        <v>172.9973999999999</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>161-173</t>
+          <t>161-172</t>
         </is>
       </c>
     </row>
@@ -583,14 +583,14 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>165.2879500000001</v>
+        <v>164.8889000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>181.9311000000002</v>
+        <v>182.4804000000002</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>165-181</t>
+          <t>164-182</t>
         </is>
       </c>
     </row>
@@ -601,14 +601,14 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>171.7995</v>
+        <v>171.8649000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>188.1008</v>
+        <v>187.8340000000001</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>171-188</t>
+          <t>171-187</t>
         </is>
       </c>
     </row>
@@ -619,14 +619,14 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>179.207</v>
+        <v>179.7237499999999</v>
       </c>
       <c r="C11" t="n">
-        <v>213.1596000000001</v>
+        <v>212.5638</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>179-213</t>
+          <t>179-212</t>
         </is>
       </c>
     </row>
@@ -637,14 +637,14 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>202.4219999999997</v>
+        <v>201.4459999999997</v>
       </c>
       <c r="C12" t="n">
-        <v>231.4146</v>
+        <v>230.0788000000001</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>202-231</t>
+          <t>201-230</t>
         </is>
       </c>
     </row>
@@ -655,10 +655,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>222.8079999999998</v>
+        <v>222.9420000000001</v>
       </c>
       <c r="C13" t="n">
-        <v>262.6869999999999</v>
+        <v>262.8849999999999</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/club_ranges.xlsx
+++ b/club_ranges.xlsx
@@ -457,10 +457,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>42.496</v>
+        <v>42.40550000000003</v>
       </c>
       <c r="C2" t="n">
-        <v>83.41199999999998</v>
+        <v>83.63939999999995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>81.83624999999995</v>
+        <v>78.85500000000008</v>
       </c>
       <c r="C3" t="n">
-        <v>109.8654000000001</v>
+        <v>100.492</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>81-109</t>
+          <t>78-100</t>
         </is>
       </c>
     </row>
@@ -493,14 +493,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>106.2040000000001</v>
+        <v>102.771</v>
       </c>
       <c r="C4" t="n">
-        <v>127.5999999999999</v>
+        <v>124.1584</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>106-127</t>
+          <t>102-124</t>
         </is>
       </c>
     </row>
@@ -511,14 +511,14 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>127.8786</v>
+        <v>121.8544999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>142.8230999999999</v>
+        <v>140.2331000000001</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>127-142</t>
+          <t>121-140</t>
         </is>
       </c>
     </row>
@@ -529,14 +529,14 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>137.7482999999998</v>
+        <v>135.6292499999998</v>
       </c>
       <c r="C6" t="n">
-        <v>153.1431999999999</v>
+        <v>149.8178000000001</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>137-153</t>
+          <t>135-149</t>
         </is>
       </c>
     </row>
@@ -547,14 +547,14 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>150.2533499999999</v>
+        <v>150.5477999999998</v>
       </c>
       <c r="C7" t="n">
-        <v>165.37325</v>
+        <v>162.72065</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>150-165</t>
+          <t>150-162</t>
         </is>
       </c>
     </row>
@@ -565,14 +565,14 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>161.3094</v>
+        <v>159.0025999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>172.9973999999999</v>
+        <v>172.8574</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>161-172</t>
+          <t>159-172</t>
         </is>
       </c>
     </row>
@@ -583,14 +583,14 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>164.8889000000001</v>
+        <v>165.1000000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>182.4804000000002</v>
+        <v>182.1174000000002</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>164-182</t>
+          <t>165-182</t>
         </is>
       </c>
     </row>
@@ -601,14 +601,14 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>171.8649000000001</v>
+        <v>171.8997</v>
       </c>
       <c r="C10" t="n">
-        <v>187.8340000000001</v>
+        <v>188.0209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>171-187</t>
+          <t>171-188</t>
         </is>
       </c>
     </row>
@@ -619,14 +619,14 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>179.7237499999999</v>
+        <v>180.5397499999999</v>
       </c>
       <c r="C11" t="n">
-        <v>212.5638</v>
+        <v>214.8974499999999</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>179-212</t>
+          <t>180-214</t>
         </is>
       </c>
     </row>
@@ -637,14 +637,14 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>201.4459999999997</v>
+        <v>201.5219999999998</v>
       </c>
       <c r="C12" t="n">
-        <v>230.0788000000001</v>
+        <v>231.4766000000002</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>201-230</t>
+          <t>201-231</t>
         </is>
       </c>
     </row>
@@ -655,14 +655,14 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>222.9420000000001</v>
+        <v>222.1259999999998</v>
       </c>
       <c r="C13" t="n">
-        <v>262.8849999999999</v>
+        <v>263.1299999999998</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>222-262</t>
+          <t>222-263</t>
         </is>
       </c>
     </row>

--- a/club_ranges.xlsx
+++ b/club_ranges.xlsx
@@ -457,14 +457,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>42.40550000000003</v>
+        <v>43.3645</v>
       </c>
       <c r="C2" t="n">
-        <v>83.63939999999995</v>
+        <v>89.12169999999998</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>42-83</t>
+          <t>43-89</t>
         </is>
       </c>
     </row>
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>78.85500000000008</v>
+        <v>79.26800000000004</v>
       </c>
       <c r="C3" t="n">
-        <v>100.492</v>
+        <v>100.764</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>78-100</t>
+          <t>79-100</t>
         </is>
       </c>
     </row>
@@ -493,14 +493,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>102.771</v>
+        <v>102.554</v>
       </c>
       <c r="C4" t="n">
-        <v>124.1584</v>
+        <v>123.3372000000001</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>102-124</t>
+          <t>102-123</t>
         </is>
       </c>
     </row>
@@ -511,14 +511,14 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>121.8544999999999</v>
+        <v>122.8123</v>
       </c>
       <c r="C5" t="n">
-        <v>140.2331000000001</v>
+        <v>139.0272000000001</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>121-140</t>
+          <t>122-139</t>
         </is>
       </c>
     </row>
@@ -529,14 +529,14 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>135.6292499999998</v>
+        <v>133.6712999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>149.8178000000001</v>
+        <v>149.7159999999998</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>135-149</t>
+          <t>133-149</t>
         </is>
       </c>
     </row>
@@ -547,14 +547,14 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>150.5477999999998</v>
+        <v>148.8272500000001</v>
       </c>
       <c r="C7" t="n">
-        <v>162.72065</v>
+        <v>161.3110000000001</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>150-162</t>
+          <t>148-161</t>
         </is>
       </c>
     </row>
@@ -565,14 +565,14 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>159.0025999999999</v>
+        <v>156.6791999999998</v>
       </c>
       <c r="C8" t="n">
-        <v>172.8574</v>
+        <v>173.4231</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>159-172</t>
+          <t>156-173</t>
         </is>
       </c>
     </row>
@@ -583,14 +583,14 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>165.1000000000001</v>
+        <v>164.0824</v>
       </c>
       <c r="C9" t="n">
-        <v>182.1174000000002</v>
+        <v>181.3310000000002</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>165-182</t>
+          <t>164-181</t>
         </is>
       </c>
     </row>
@@ -601,14 +601,14 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>171.8997</v>
+        <v>173.7672999999999</v>
       </c>
       <c r="C10" t="n">
-        <v>188.0209</v>
+        <v>188.5556000000001</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>171-188</t>
+          <t>173-188</t>
         </is>
       </c>
     </row>
@@ -619,14 +619,14 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>180.5397499999999</v>
+        <v>181.5264999999998</v>
       </c>
       <c r="C11" t="n">
-        <v>214.8974499999999</v>
+        <v>218.3850000000001</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>180-214</t>
+          <t>181-218</t>
         </is>
       </c>
     </row>
@@ -637,14 +637,14 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>201.5219999999998</v>
+        <v>205.0297499999998</v>
       </c>
       <c r="C12" t="n">
-        <v>231.4766000000002</v>
+        <v>232.64165</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>201-231</t>
+          <t>205-232</t>
         </is>
       </c>
     </row>
@@ -655,10 +655,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>222.1259999999998</v>
+        <v>222.0915000000001</v>
       </c>
       <c r="C13" t="n">
-        <v>263.1299999999998</v>
+        <v>263.7140000000005</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/club_ranges.xlsx
+++ b/club_ranges.xlsx
@@ -1,37 +1,129 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+  <si>
+    <t>Club</t>
+  </si>
+  <si>
+    <t>Lower</t>
+  </si>
+  <si>
+    <t>Upper</t>
+  </si>
+  <si>
+    <t>Range</t>
+  </si>
+  <si>
+    <t>lw</t>
+  </si>
+  <si>
+    <t>sw</t>
+  </si>
+  <si>
+    <t>gw</t>
+  </si>
+  <si>
+    <t>pw</t>
+  </si>
+  <si>
+    <t>9i</t>
+  </si>
+  <si>
+    <t>8i</t>
+  </si>
+  <si>
+    <t>7i</t>
+  </si>
+  <si>
+    <t>6i</t>
+  </si>
+  <si>
+    <t>5i</t>
+  </si>
+  <si>
+    <t>3h</t>
+  </si>
+  <si>
+    <t>3w</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>43-89</t>
+  </si>
+  <si>
+    <t>79-100</t>
+  </si>
+  <si>
+    <t>102-123</t>
+  </si>
+  <si>
+    <t>122-139</t>
+  </si>
+  <si>
+    <t>133-149</t>
+  </si>
+  <si>
+    <t>148-161</t>
+  </si>
+  <si>
+    <t>156-173</t>
+  </si>
+  <si>
+    <t>164-181</t>
+  </si>
+  <si>
+    <t>173-188</t>
+  </si>
+  <si>
+    <t>181-218</t>
+  </si>
+  <si>
+    <t>205-232</t>
+  </si>
+  <si>
+    <t>222-263</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +138,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,253 +454,193 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Club</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Lower</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Upper</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Range</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>lw</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
         <v>43.3645</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>89.12169999999998</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>43-89</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>sw</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
         <v>79.26800000000004</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>100.764</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>79-100</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>gw</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
         <v>102.554</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>123.3372000000001</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>102-123</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>pw</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5">
         <v>122.8123</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>139.0272000000001</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>122-139</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>9i</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
         <v>133.6712999999999</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>149.7159999999998</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>133-149</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>8i</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+      <c r="D6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
         <v>148.8272500000001</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>161.3110000000001</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>148-161</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>7i</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+      <c r="D7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
         <v>156.6791999999998</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>173.4231</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>156-173</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>6i</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+      <c r="D8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
         <v>164.0824</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>181.3310000000002</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>164-181</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>5i</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10">
         <v>173.7672999999999</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>188.5556000000001</v>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>173-188</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>3h</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+      <c r="D10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11">
         <v>181.5264999999998</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>218.3850000000001</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>181-218</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>3w</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12">
         <v>205.0297499999998</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>232.64165</v>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>205-232</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
+      <c r="D12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13">
         <v>222.0915000000001</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>263.7140000000005</v>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>222-263</t>
-        </is>
+      <c r="D13" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>